--- a/result/result_3.xlsx
+++ b/result/result_3.xlsx
@@ -127,6 +127,111 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -416,13 +521,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,21 +542,41 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>问题类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SQL 查询语句</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>图形格式</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>图表</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>研报截图</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>B2001</t>
@@ -455,30 +584,91 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>多意图</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>[{"Q": "2024年利润最高的top10企业是哪些？这些企业的利润、销售额年同比是多少？年同比上涨幅度最大的是哪家企业？"}]</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period='FY' ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>{
   "问题编号": "B2001",
   "问题类型": "多意图",
-  "子任务结果": [
+  "结构化结果": [
     {
       "子任务": "t1",
       "意图": "rank",
       "Q": "2024年利润最高的top10企业是哪些？这些企业的利润、销售额年同比是多少？年同比上涨幅度最大的是哪家企业？",
-      "SQL": "",
-      "结构化结果": []
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period='FY' ORDER BY net_profit DESC LIMIT 10",
+      "图形格式": "bar",
+      "结果数据": [
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "FY",
+          "net_profit": 377774.13,
+          "_period": "2024年报"
+        },
+        {
+          "stock_abbr": "金花股份",
+          "report_year": 2024,
+          "report_period": "FY",
+          "net_profit": 7360.05,
+          "_period": "2024年报"
+        }
+      ],
+      "image": "B2001_1.jpg"
+    },
+    {
+      "子任务": "t2",
+      "意图": "compare",
+      "Q": "2024年利润最高的top10企业是哪些？这些企业的利润、销售额年同比是多少？年同比上涨幅度最大的是哪家企业？",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period='FY' ORDER BY net_profit DESC LIMIT 10",
+      "图形格式": "bar",
+      "结果数据": [
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "FY",
+          "net_profit": 377774.13,
+          "_period": "2024年报"
+        },
+        {
+          "stock_abbr": "金花股份",
+          "report_year": 2024,
+          "report_period": "FY",
+          "net_profit": 7360.05,
+          "_period": "2024年报"
+        }
+      ],
+      "image": "B2001_2.jpg"
     }
   ],
   "references": []
 }</t>
         </is>
       </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>B2001_2.jpg</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>B2002</t>
@@ -486,30 +676,71 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>意图模糊</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>[{"Q": "国家医保目录新增的中药产品有哪些"}]</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>{
   "问题编号": "B2002",
   "问题类型": "意图模糊",
-  "子任务结果": [
+  "结构化结果": [
     {
       "子任务": "t1",
       "意图": "query",
       "Q": "国家医保目录新增的中药产品有哪些",
       "SQL": "",
-      "结构化结果": []
+      "图形格式": "table",
+      "结果数据": [],
+      "image": ""
+    },
+    {
+      "子任务": "t1_rag",
+      "意图": "attribution",
+      "Q": "国家医保目录新增的中药产品有哪些",
+      "答案": "- 医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化（p3）: 开水冲服。1次1袋，\n7 新疆银朵兰药业 复方比那甫西颗粒 当于饮片2.67g,含甘草浸 中药1.1类\n塞、流涕、咽痛、头痛、口干等。 一日2次。疗程3天。\n膏649mg))\n来源：国家医保局，国金证券研究所\n投资建议\n西药：建议关注纳入新；- 医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化（p2）: 扫码获取更多服务\n行业点评\n 凭借相关药物的医保准入，有望实现产品放量与市场份额的快速提升。本轮医保谈判中西药涉及的107个品类，\n合计116款药物（部分同一品类有多家药企入选）。其中恒瑞医药合计11款新药首次纳入医保目录，其次是阿斯\n利"
     }
   ],
-  "references": []
+  "references": [
+    {
+      "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/行业研报/医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化.pdf",
+      "paper_title": "医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化",
+      "page": 3,
+      "score": 0.1616,
+      "text": "开水冲服。1次1袋，\n7 新疆银朵兰药业 复方比那甫西颗粒 当于饮片2.67g,含甘草浸 中药1.1类\n塞、流涕、咽痛、头痛、口干等。 一日2次。疗程3天。\n膏649mg))\n来源：国家医保局，国金证券研究所\n投资建议\n西药：建议关注纳入新版医保目录创新药较多/品种重磅的恒瑞医药、百济神州、康方生物、科伦博泰、信达生物等，\n以及大单品首次纳入医保的康诺亚（IL4单抗）、特宝生物（长效生长激素）等。\n中成药：建议关注入选新版医保目录的中药产品放量潜力，如华润三九的益气清肺颗粒、以岭药业的芪防鼻通片、方\n盛制药的养血祛风止痛颗粒、康缘药业的玉女煎颗粒/温阳解毒颗粒等。\n敬请参阅最后一页特别声明",
+      "paper_image": "refs/医药健康行业研究_从2025医保谈判看行业风向_成功率提升，创新导向持续强化_p3.jpg"
+    },
+    {
+      "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/行业研报/医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化.pdf",
+      "paper_title": "医药健康行业研究：从2025医保谈判看行业风向：成功率提升，创新导向持续强化",
+      "page": 2,
+      "score": 0.1473,
+      "text": "扫码获取更多服务\n行业点评\n 凭借相关药物的医保准入，有望实现产品放量与市场份额的快速提升。本轮医保谈判中西药涉及的107个品类，\n合计116款药物（部分同一品类有多家药企入选）。其中恒瑞医药合计11款新药首次纳入医保目录，其次是阿斯\n利康合计纳入4款，正大天晴、科伦博泰、礼来制药、齐鲁制药、罗氏制药则分别成功纳入3款药物。\n图表5：恒瑞医药合计11款新药首次纳入医保目录\n12 11\n10\n8\n6\n4\n4 3 3 3 3 3\n2 2 2 2 2 2 2 2 2 2\n2 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1",
+      "paper_image": "refs/医药健康行业研究_从2025医保谈判看行业风向_成功率提升，创新导向持续强化_p2.jpg"
+    }
+  ]
 }</t>
         </is>
       </c>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>refs/医药健康行业研究_从2025医保谈判看行业风向_成功率提升，创新导向持续强化_p3.jpg</t>
+        </is>
+      </c>
     </row>
-    <row r="4">
+    <row r="4" ht="120" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>B2003</t>
@@ -517,26 +748,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
+          <t>归因分析</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>[{"Q": "华润三九近三年的主营业务收入情况做可视化绘图"}, {"Q": "主营业务收入上升的原因是什么"}]</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='华润三九') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
-        </is>
-      </c>
       <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>{
   "问题编号": "B2003",
   "问题类型": "归因分析",
-  "子任务结果": [
+  "结构化结果": [
     {
       "子任务": "t1",
       "意图": "trend",
       "Q": "华润三九近三年的主营业务收入情况做可视化绘图",
       "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='华润三九') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
-      "结构化结果": [
+      "图形格式": "line",
+      "结果数据": [
         {
           "stock_abbr": "华润三九",
           "report_year": 2022,
@@ -607,20 +849,94 @@
           "total_operating_revenue": 685365.64,
           "_period": "2025一季报"
         }
-      ]
+      ],
+      "image": "B2003_1.jpg"
     },
     {
       "子任务": "t1",
       "意图": "query",
       "Q": "主营业务收入上升的",
-      "SQL": "",
-      "结构化结果": []
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "图形格式": "table",
+      "结果数据": [
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2022,
+          "report_period": "FY",
+          "total_operating_revenue": 1807946.15,
+          "_period": "2022年报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2023,
+          "report_period": "Q1",
+          "total_operating_revenue": 635240.83,
+          "_period": "2023一季报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2023,
+          "report_period": "HY",
+          "total_operating_revenue": 1314612.57,
+          "_period": "2023半年报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2023,
+          "report_period": "Q3",
+          "total_operating_revenue": null,
+          "_period": "2023三季报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2023,
+          "report_period": "FY",
+          "total_operating_revenue": 2473896.33,
+          "_period": "2023年报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "Q1",
+          "total_operating_revenue": 729407.06,
+          "_period": "2024一季报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "HY",
+          "total_operating_revenue": 1410601.28,
+          "_period": "2024半年报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "Q3",
+          "total_operating_revenue": null,
+          "_period": "2024三季报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2024,
+          "report_period": "FY",
+          "total_operating_revenue": 2761661.18,
+          "_period": "2024年报"
+        },
+        {
+          "stock_abbr": "华润三九",
+          "report_year": 2025,
+          "report_period": "Q1",
+          "total_operating_revenue": 685365.64,
+          "_period": "2025一季报"
+        }
+      ],
+      "image": "B2003_2.jpg"
     },
     {
       "子任务": "t2",
       "意图": "attribution",
       "Q": "主营业务收入上升的原因是什么",
-      "答案": "- 业绩表现稳健，彰显强经营韧性与品牌力（p2）: 扫码获取更多服务\n公司点评\n附录：三张报表预测摘要\n损益表（人民币百万元） 资产负债表（人民币百万元）\n2022 2023 2024 2025E 2026E 2027E 2022 2023 2024 2025E 2026E 2027E\n主营\n- 业绩表现稳健，彰显强经营韧性与品牌力（p4）: 、单位或附属机构在制作类似的其他材料时所给出的意\n见不同或者相反。\n本报告仅为参考之用，在任何地区均不应被视为买卖任何证券、金融工具的要约或要约邀请。本报告提及的任何证券或金融工具均可能含有重大的风险，可能\n不易变卖以及不适合所有投资者。本\n- 业绩表现稳健，彰显强经营韧性与品牌力（p1）: 业绩简评\n2025 年10 月 24 日，公司发布2025 年第三季度报告。2025年前\n三季度，公司实现收入219.9 亿元，同比+11.38%；实现归母净利\n润23.5 亿元，同比-20.51%；实现扣非归母净利润21.9亿元，同\n比-"
+      "答案": "- 业绩表现稳健，彰显强经营韧性与品牌力（p2）: 扫码获取更多服务\n公司点评\n附录：三张报表预测摘要\n损益表（人民币百万元） 资产负债表（人民币百万元）\n2022 2023 2024 2025E 2026E 2027E 2022 2023 2024 2025E 2026E 2027E\n主营；- 2025年三季报点评：内涵+外延双轮驱动，经营拐点已现（p2）: 华润三九（000999）2025年三季报点评\n附表：财务预测与估值\n[利T润ab表l（e百_P万r元of）i tDet2a02i4lA] 2025E 2026E 2027E 现金流量表（百万元） 2024A 2025E 2026E 2027；- 业绩表现稳健，彰显强经营韧性与品牌力（p4）: 扫码获取更多服务\n公司点评\n特别声明：\n国金证券股份有限公司经中国证券监督管理委员会批准，已具备证券投资咨询业务资格。\n形式的复制、转发、转载、引用、修改、仿制、刊发，或以任何侵犯本公司版权的其他方式使用。经过书面授权的引用、刊发，需注明出"
     }
   ],
   "references": [
@@ -628,32 +944,43 @@
       "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/个股研报/业绩表现稳健，彰显强经营韧性与品牌力.pdf",
       "paper_title": "业绩表现稳健，彰显强经营韧性与品牌力",
       "page": 2,
-      "score": 0.0795,
-      "text": "扫码获取更多服务\n公司点评\n附录：三张报表预测摘要\n损益表（人民币百万元） 资产负债表（人民币百万元）\n2022 2023 2024 2025E 2026E 2027E 2022 2023 2024 2025E 2026E 2027E\n主营业务收入 18,079 24,739 27,617 30,449 33,700 37,212 货币资金 3,150 6,771 5,017 5,172 7,074 9,328\n增长率 36.8% 11.6% 10.3% 10.7% 10.4% 应收款项 5,696 8,148 9,199 9,853 10,642 11,465\n主营业务成本 -8,313 -11,567 -13,296 -13,859 -14,970 -16,329 存货 2,499 5,112 4,933 6,202 6,431 6,761\n%销售收入 46.0% 46.8% 48.1% 45.5% 44.4% 43.9% 其他流动资产 644 2,491 2,727 2,870 2,896 2,912\n毛利 9,766 13,172 14,",
-      "paper_image": ""
+      "score": 0.2789,
+      "text": "扫码获取更多服务\n公司点评\n附录：三张报表预测摘要\n损益表（人民币百万元） 资产负债表（人民币百万元）\n2022 2023 2024 2025E 2026E 2027E 2022 2023 2024 2025E 2026E 2027E\n主营业务收入 18,079 24,739 27,617 30,449 33,700 37,212 货币资金 3,150 6,771 5,017 5,172 7,074 9,328\n增长率 36.8% 11.6% 10.3% 10.7% 10.4% 应收款项 5,696 8,148 9,199 9,853 10,642 11,465\n主营业务成本 -8,313 -",
+      "paper_image": "refs/业绩表现稳健，彰显强经营韧性与品牌力_p2.jpg"
+    },
+    {
+      "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/个股研报/2025年三季报点评：内涵+外延双轮驱动，经营拐点已现.pdf",
+      "paper_title": "2025年三季报点评：内涵+外延双轮驱动，经营拐点已现",
+      "page": 2,
+      "score": 0.1751,
+      "text": "华润三九（000999）2025年三季报点评\n附表：财务预测与估值\n[利T润ab表l（e百_P万r元of）i tDet2a02i4lA] 2025E 2026E 2027E 现金流量表（百万元） 2024A 2025E 2026E 2027E\n营业收入 27616.61 30828.99 34374.43 38368.48 净利润 3777.74 3893.04 4370.74 4894.56\n营业成本 13295.62 14398.71 15843.35 17458.02 折旧与摊销 815.15 1137.02 1239.58 1365.44\n营业税金及附加 294.78 400.78 4",
+      "paper_image": "refs/2025年三季报点评_内涵+外延双轮驱动，经营拐点已现_p2.jpg"
     },
     {
       "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/个股研报/业绩表现稳健，彰显强经营韧性与品牌力.pdf",
       "paper_title": "业绩表现稳健，彰显强经营韧性与品牌力",
       "page": 4,
-      "score": 0.069,
-      "text": "、单位或附属机构在制作类似的其他材料时所给出的意\n见不同或者相反。\n本报告仅为参考之用，在任何地区均不应被视为买卖任何证券、金融工具的要约或要约邀请。本报告提及的任何证券或金融工具均可能含有重大的风险，可能\n不易变卖以及不适合所有投资者。本报告所提及的证券或金融工具的价格、价值及收益可能会受汇率影响而波动。过往的业绩并不能代表未来的表现。\n客户应当考虑到国金证券存在可能影响本报告客观性的利益冲突，而不应视本报告为作出投资决策的唯一因素。证券研究报告是用于服务具备专业知识的投资\n者和投资顾问的专业产品，使用时必须经专业人士进行解读。国金证券建议获取报告人员应考虑本报告的任何意见或建议是否符合其特定状况，以及（若有必要）\n咨询独立投资顾问。报告本身、报告中的信息或所表达意见也不构成投资、法律、会计或税务的最终操作建议，国金证券不就报告中的内容对最终操作建议做出任\n何担保，在任何时候均不构成对任何人的个人推荐。\n在法律允许的情况下，国金证券的关联机构可能会持有报告中涉及的公司所发行的证券并进行交易，并可能为这些公司正在提供或争取提供多种金融服务。\n本报",
-      "paper_image": ""
-    },
-    {
-      "paper_path": "/home/user/rstats/data/B题-示例数据/附件5：研报数据/个股研报/业绩表现稳健，彰显强经营韧性与品牌力.pdf",
-      "paper_title": "业绩表现稳健，彰显强经营韧性与品牌力",
-      "page": 1,
-      "score": 0.0626,
-      "text": "业绩简评\n2025 年10 月 24 日，公司发布2025 年第三季度报告。2025年前\n三季度，公司实现收入219.9 亿元，同比+11.38%；实现归母净利\n润23.5 亿元，同比-20.51%；实现扣非归母净利润21.9亿元，同\n比-20.56%。\n单季度看，2025年 Q3 公司实现收入 71.8 亿元，同比+27.37%；归\n母净利润 5.4 亿元，同比-4.26%；扣非归母净利润 4.9 亿元，同\n比+10.12%。\n经营分析\n流感高发季到来，全品类链条布局，CHC 业务有望持续向好。在\n度过上半年调整期后，我们预计公司内生CHC 业务在Q3企稳。公\n司已陆续上市 999 益气清肺颗粒、999 冰连清咽喷雾剂、999 玉\n屏风口服液、999 荆防颗粒等新品，其中 999 益气清肺颗粒由张\n伯礼院士及团队研发，有望填补重感康复用药空白。产品线的全\n人民币(元) 成交金额(百万元)\n面布局，有望进一步提升品牌整体市占率。Q4 流感旺季叠加公司 42.00 1,600\n1,400\n良性渠道库存，CHC 业务有望继续企稳回升。 39.00\n1",
-      "paper_image": ""
+      "score": 0.1456,
+      "text": "扫码获取更多服务\n公司点评\n特别声明：\n国金证券股份有限公司经中国证券监督管理委员会批准，已具备证券投资咨询业务资格。\n形式的复制、转发、转载、引用、修改、仿制、刊发，或以任何侵犯本公司版权的其他方式使用。经过书面授权的引用、刊发，需注明出处为“国金证券股份有限\n公司”，且不得对本报告进行任何有悖原意的删节和修改。\n本报告的产生基于国金证券及其研究人员认为可信的公开资料或实地调研资料，但国金证券及其研究人员对这些信息的准确性和完整性不作任何保证。本报告\n反映撰写研究人员的不同设想、见解及分析方法，故本报告所载观点可能与其他类似研究报告的观点及市场实际情况不一致，国金证券不对使用本报告所包含的材",
+      "paper_image": "refs/业绩表现稳健，彰显强经营韧性与品牌力_p4.jpg"
     }
   ]
 }</t>
         </is>
       </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>B2003_2.jpg</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>refs/业绩表现稳健，彰显强经营韧性与品牌力_p2.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>